--- a/XProject/Docs/Generated/FishGameTables/FishGame.xlsx
+++ b/XProject/Docs/Generated/FishGameTables/FishGame.xlsx
@@ -14,11 +14,11 @@
     <sheet name="fishspecies" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'fishbait'!$A$2:$M$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'fishdistancetier'!$A$2:$J$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'fishglobal'!$A$2:$BI$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'fishbait'!$A$2:$L$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'fishdistancetier'!$A$2:$I$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'fishglobal'!$A$2:$BH$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'fishrod'!$A$2:$J$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'fishspecies'!$A$2:$T$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'fishspecies'!$A$2:$S$14</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -454,7 +454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:L7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -467,9 +467,8 @@
     <col width="17" customWidth="1" min="8" max="8"/>
     <col width="22" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -525,15 +524,10 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>解锁鱼竿等级</t>
+          <t>启用阶段</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>启用阶段</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>可购买</t>
         </is>
@@ -592,15 +586,10 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>UnlockRodLevel</t>
+          <t>EnabledPhase</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>EnabledPhase</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>CanPurchase</t>
         </is>
@@ -644,10 +633,7 @@
       <c r="K3" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="L3" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="M3" s="3" t="inlineStr">
+      <c r="L3" s="3" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
@@ -689,12 +675,9 @@
         <v>0.9</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="L4" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="M4" s="3" t="inlineStr">
+      <c r="L4" s="3" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -736,12 +719,9 @@
         <v>0.82</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="L5" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="M5" s="3" t="inlineStr">
+      <c r="L5" s="3" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -783,12 +763,9 @@
         <v>0.76</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="L6" s="3" t="n">
         <v>99</v>
       </c>
-      <c r="M6" s="3" t="inlineStr">
+      <c r="L6" s="3" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
@@ -830,19 +807,16 @@
         <v>0.7</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="L7" s="3" t="n">
         <v>99</v>
       </c>
-      <c r="M7" s="3" t="inlineStr">
+      <c r="L7" s="3" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:M7"/>
+  <autoFilter ref="A2:L7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -853,68 +827,62 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="23" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="23" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>距离档位ID</t>
+          <t>最小距离</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>最小距离</t>
+          <t>最大距离</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>最大距离</t>
+          <t>可咬钩</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>可咬钩</t>
+          <t>鱼等级权重加成</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>鱼等级权重加成</t>
+          <t>普通稀有度权重</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>普通稀有度权重</t>
+          <t>少见稀有度权重</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>少见稀有度权重</t>
+          <t>稀有度权重</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>稀有度权重</t>
+          <t>传说稀有度权重</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>传说稀有度权重</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>等待时间倍率</t>
         </is>
@@ -923,50 +891,45 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>TierId</t>
+          <t>MinDistance</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>MinDistance</t>
+          <t>MaxDistance</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>MaxDistance</t>
+          <t>CanBite</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>CanBite</t>
+          <t>FishLevelWeightBonus</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>FishLevelWeightBonus</t>
+          <t>RarityWeightCommon</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>RarityWeightCommon</t>
+          <t>RarityWeightUncommon</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>RarityWeightUncommon</t>
+          <t>RarityWeightRare</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>RarityWeightRare</t>
+          <t>RarityWeightLegendary</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>RarityWeightLegendary</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>WaitTimeMultiplier</t>
         </is>
@@ -974,24 +937,24 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="3" t="n">
+      <c r="F3" s="3" t="n">
         <v>0</v>
-      </c>
-      <c r="C3" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" s="3" t="n">
-        <v>1</v>
       </c>
       <c r="G3" s="3" t="n">
         <v>0</v>
@@ -1000,116 +963,104 @@
         <v>0</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" s="3" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="n">
-        <v>2</v>
+        <v>5.01</v>
       </c>
       <c r="B4" s="3" t="n">
-        <v>5.01</v>
-      </c>
-      <c r="C4" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
+      <c r="D4" s="3" t="n">
+        <v>0.02</v>
+      </c>
       <c r="E4" s="3" t="n">
-        <v>0.02</v>
+        <v>1</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1</v>
+        <v>0.65</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>0.65</v>
+        <v>0.3</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>0.3</v>
+        <v>0.08</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="J4" s="3" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
-        <v>3</v>
+        <v>15.01</v>
       </c>
       <c r="B5" s="3" t="n">
-        <v>15.01</v>
-      </c>
-      <c r="C5" s="3" t="n">
         <v>28</v>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
+      <c r="D5" s="3" t="n">
+        <v>0.08</v>
+      </c>
       <c r="E5" s="3" t="n">
-        <v>0.08</v>
+        <v>0.85</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>0.85</v>
+        <v>0.92</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>0.92</v>
+        <v>0.6</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>0.6</v>
+        <v>0.16</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="J5" s="3" t="n">
         <v>0.92</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="n">
-        <v>4</v>
+        <v>28.01</v>
       </c>
       <c r="B6" s="3" t="n">
-        <v>28.01</v>
-      </c>
-      <c r="C6" s="3" t="n">
         <v>40</v>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
+      <c r="D6" s="3" t="n">
+        <v>0.16</v>
+      </c>
       <c r="E6" s="3" t="n">
-        <v>0.16</v>
+        <v>0.72</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.72</v>
+        <v>1</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>0.92</v>
+        <v>0.32</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="J6" s="3" t="n">
         <v>0.84</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:J6"/>
+  <autoFilter ref="A2:I6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1120,7 +1071,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI3"/>
+  <dimension ref="A1:BH3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1140,50 +1091,49 @@
     <col width="15" customWidth="1" min="15" max="15"/>
     <col width="22" customWidth="1" min="16" max="16"/>
     <col width="16" customWidth="1" min="17" max="17"/>
-    <col width="16" customWidth="1" min="18" max="18"/>
+    <col width="27" customWidth="1" min="18" max="18"/>
     <col width="27" customWidth="1" min="19" max="19"/>
-    <col width="27" customWidth="1" min="20" max="20"/>
-    <col width="16" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
-    <col width="23" customWidth="1" min="23" max="23"/>
-    <col width="14" customWidth="1" min="24" max="24"/>
-    <col width="22" customWidth="1" min="25" max="25"/>
-    <col width="21" customWidth="1" min="26" max="26"/>
-    <col width="18" customWidth="1" min="27" max="27"/>
-    <col width="25" customWidth="1" min="28" max="28"/>
-    <col width="26" customWidth="1" min="29" max="29"/>
-    <col width="24" customWidth="1" min="30" max="30"/>
+    <col width="16" customWidth="1" min="20" max="20"/>
+    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="23" customWidth="1" min="22" max="22"/>
+    <col width="14" customWidth="1" min="23" max="23"/>
+    <col width="22" customWidth="1" min="24" max="24"/>
+    <col width="21" customWidth="1" min="25" max="25"/>
+    <col width="18" customWidth="1" min="26" max="26"/>
+    <col width="25" customWidth="1" min="27" max="27"/>
+    <col width="26" customWidth="1" min="28" max="28"/>
+    <col width="24" customWidth="1" min="29" max="29"/>
+    <col width="20" customWidth="1" min="30" max="30"/>
     <col width="20" customWidth="1" min="31" max="31"/>
-    <col width="20" customWidth="1" min="32" max="32"/>
-    <col width="23" customWidth="1" min="33" max="33"/>
+    <col width="23" customWidth="1" min="32" max="32"/>
+    <col width="35" customWidth="1" min="33" max="33"/>
     <col width="35" customWidth="1" min="34" max="34"/>
-    <col width="35" customWidth="1" min="35" max="35"/>
-    <col width="27" customWidth="1" min="36" max="36"/>
+    <col width="27" customWidth="1" min="35" max="35"/>
+    <col width="31" customWidth="1" min="36" max="36"/>
     <col width="31" customWidth="1" min="37" max="37"/>
-    <col width="31" customWidth="1" min="38" max="38"/>
+    <col width="22" customWidth="1" min="38" max="38"/>
     <col width="22" customWidth="1" min="39" max="39"/>
-    <col width="22" customWidth="1" min="40" max="40"/>
+    <col width="25" customWidth="1" min="40" max="40"/>
     <col width="25" customWidth="1" min="41" max="41"/>
-    <col width="25" customWidth="1" min="42" max="42"/>
+    <col width="21" customWidth="1" min="42" max="42"/>
     <col width="21" customWidth="1" min="43" max="43"/>
-    <col width="21" customWidth="1" min="44" max="44"/>
-    <col width="23" customWidth="1" min="45" max="45"/>
-    <col width="24" customWidth="1" min="46" max="46"/>
-    <col width="26" customWidth="1" min="47" max="47"/>
-    <col width="25" customWidth="1" min="48" max="48"/>
-    <col width="20" customWidth="1" min="49" max="49"/>
-    <col width="26" customWidth="1" min="50" max="50"/>
-    <col width="24" customWidth="1" min="51" max="51"/>
+    <col width="23" customWidth="1" min="44" max="44"/>
+    <col width="24" customWidth="1" min="45" max="45"/>
+    <col width="26" customWidth="1" min="46" max="46"/>
+    <col width="25" customWidth="1" min="47" max="47"/>
+    <col width="20" customWidth="1" min="48" max="48"/>
+    <col width="26" customWidth="1" min="49" max="49"/>
+    <col width="24" customWidth="1" min="50" max="50"/>
+    <col width="28" customWidth="1" min="51" max="51"/>
     <col width="28" customWidth="1" min="52" max="52"/>
-    <col width="28" customWidth="1" min="53" max="53"/>
-    <col width="25" customWidth="1" min="54" max="54"/>
-    <col width="21" customWidth="1" min="55" max="55"/>
-    <col width="17" customWidth="1" min="56" max="56"/>
-    <col width="19" customWidth="1" min="57" max="57"/>
-    <col width="25" customWidth="1" min="58" max="58"/>
-    <col width="23" customWidth="1" min="59" max="59"/>
-    <col width="21" customWidth="1" min="60" max="60"/>
-    <col width="25" customWidth="1" min="61" max="61"/>
+    <col width="25" customWidth="1" min="53" max="53"/>
+    <col width="21" customWidth="1" min="54" max="54"/>
+    <col width="17" customWidth="1" min="55" max="55"/>
+    <col width="19" customWidth="1" min="56" max="56"/>
+    <col width="25" customWidth="1" min="57" max="57"/>
+    <col width="23" customWidth="1" min="58" max="58"/>
+    <col width="21" customWidth="1" min="59" max="59"/>
+    <col width="25" customWidth="1" min="60" max="60"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1274,220 +1224,215 @@
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>锁线消耗加成</t>
+          <t>挣扎放线消耗倍率</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>挣扎放线消耗倍率</t>
+          <t>控制压制换算除数</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>控制压制换算除数</t>
+          <t>冲刺力度倍率</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>冲刺力度倍率</t>
+          <t>休息力度倍率</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>休息力度倍率</t>
+          <t>最大抛竿蓄力时长</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>最大抛竿蓄力时长</t>
+          <t>抛竿延迟</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>抛竿延迟</t>
+          <t>张力缓和时长</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>张力缓和时长</t>
+          <t>收线张力速度倍率</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>收线张力速度倍率</t>
+          <t>最低收线速度</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>最低收线速度</t>
+          <t>常规捕获窗口偏移</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>常规捕获窗口偏移</t>
+          <t>疲劳捕获窗口偏移</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>疲劳捕获窗口偏移</t>
+          <t>冲刺准备体力阈值</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>冲刺准备体力阈值</t>
+          <t>冲刺准备最短延迟</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>冲刺准备最短延迟</t>
+          <t>冲刺准备最长延迟</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>冲刺准备最长延迟</t>
+          <t>冲刺收线危险窗口</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>冲刺收线危险窗口</t>
+          <t>冲刺收线危险张力下限</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>冲刺收线危险张力下限</t>
+          <t>冲刺收线危险张力上限</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>冲刺收线危险张力上限</t>
+          <t>冲刺收线进度上限比例</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>冲刺收线进度上限比例</t>
+          <t>冲刺收线阻力惩罚下限</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>冲刺收线阻力惩罚下限</t>
+          <t>冲刺收线阻力惩罚上限</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>冲刺收线阻力惩罚上限</t>
+          <t>重量体力插值下限</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>重量体力插值下限</t>
+          <t>重量体力插值上限</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>重量体力插值上限</t>
+          <t>重量阻力插值下限</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>重量阻力插值下限</t>
+          <t>重量阻力插值上限</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>重量阻力插值上限</t>
+          <t>重量逃逸插值下限</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>重量逃逸插值下限</t>
+          <t>重量逃逸插值上限</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>重量逃逸插值上限</t>
+          <t>平稳阶段力度插值权重</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>平稳阶段力度插值权重</t>
+          <t>冲刺阶段张力消耗倍率</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>冲刺阶段张力消耗倍率</t>
+          <t>疲劳阶段张力插值权重</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>疲劳阶段张力插值权重</t>
+          <t>平稳阶段张力消耗倍率</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>平稳阶段张力消耗倍率</t>
+          <t>收线阻力基础值</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>收线阻力基础值</t>
+          <t>收线阻力消耗倍率</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>收线阻力消耗倍率</t>
+          <t>冲刺收线挣扎倍率</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>冲刺收线挣扎倍率</t>
+          <t>疲劳收线阻力下限</t>
         </is>
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
-          <t>疲劳收线阻力下限</t>
+          <t>疲劳收线阻力倍率</t>
         </is>
       </c>
       <c r="BA1" s="1" t="inlineStr">
         <is>
-          <t>疲劳收线阻力倍率</t>
+          <t>拉力体力插值下限</t>
         </is>
       </c>
       <c r="BB1" s="1" t="inlineStr">
         <is>
-          <t>拉力体力插值下限</t>
+          <t>疲劳控制加成</t>
         </is>
       </c>
       <c r="BC1" s="1" t="inlineStr">
         <is>
-          <t>疲劳控制加成</t>
+          <t>放松增益倍率</t>
         </is>
       </c>
       <c r="BD1" s="1" t="inlineStr">
         <is>
-          <t>放松增益倍率</t>
+          <t>前期收线速度倍率</t>
         </is>
       </c>
       <c r="BE1" s="1" t="inlineStr">
         <is>
-          <t>前期收线速度倍率</t>
+          <t>等待时间倍率下限</t>
         </is>
       </c>
       <c r="BF1" s="1" t="inlineStr">
         <is>
-          <t>等待时间倍率下限</t>
+          <t>控制压制上限</t>
         </is>
       </c>
       <c r="BG1" s="1" t="inlineStr">
         <is>
-          <t>控制压制上限</t>
+          <t>平稳阶段时长倍率</t>
         </is>
       </c>
       <c r="BH1" s="1" t="inlineStr">
-        <is>
-          <t>平稳阶段时长倍率</t>
-        </is>
-      </c>
-      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>鱼饵不匹配权重倍率</t>
         </is>
@@ -1581,220 +1526,215 @@
       </c>
       <c r="R2" s="2" t="inlineStr">
         <is>
-          <t>LockDrainBonus</t>
+          <t>StruggleReleaseDrainScale</t>
         </is>
       </c>
       <c r="S2" s="2" t="inlineStr">
         <is>
-          <t>StruggleReleaseDrainScale</t>
+          <t>ControlSuppressionDivisor</t>
         </is>
       </c>
       <c r="T2" s="2" t="inlineStr">
         <is>
-          <t>ControlSuppressionDivisor</t>
+          <t>SprintForceMul</t>
         </is>
       </c>
       <c r="U2" s="2" t="inlineStr">
         <is>
-          <t>SprintForceMul</t>
+          <t>RestForceMul</t>
         </is>
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
-          <t>RestForceMul</t>
+          <t>MaxCastChargeDuration</t>
         </is>
       </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
-          <t>MaxCastChargeDuration</t>
+          <t>CastingDelay</t>
         </is>
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>CastingDelay</t>
+          <t>TensionRelaxDuration</t>
         </is>
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>TensionRelaxDuration</t>
+          <t>ReelTensionSpeedMul</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>ReelTensionSpeedMul</t>
+          <t>MinimumReelSpeed</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>MinimumReelSpeed</t>
+          <t>NormalCatchWindowOffset</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>NormalCatchWindowOffset</t>
+          <t>FatigueCatchWindowOffset</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>FatigueCatchWindowOffset</t>
+          <t>BurstReadyStaminaRatio</t>
         </is>
       </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>BurstReadyStaminaRatio</t>
+          <t>BurstReadyDelayMin</t>
         </is>
       </c>
       <c r="AE2" s="2" t="inlineStr">
         <is>
-          <t>BurstReadyDelayMin</t>
+          <t>BurstReadyDelayMax</t>
         </is>
       </c>
       <c r="AF2" s="2" t="inlineStr">
         <is>
-          <t>BurstReadyDelayMax</t>
+          <t>BurstReelDangerWindow</t>
         </is>
       </c>
       <c r="AG2" s="2" t="inlineStr">
         <is>
-          <t>BurstReelDangerWindow</t>
+          <t>BurstReelDangerTensionPressureMin</t>
         </is>
       </c>
       <c r="AH2" s="2" t="inlineStr">
         <is>
-          <t>BurstReelDangerTensionPressureMin</t>
+          <t>BurstReelDangerTensionPressureMax</t>
         </is>
       </c>
       <c r="AI2" s="2" t="inlineStr">
         <is>
-          <t>BurstReelDangerTensionPressureMax</t>
+          <t>BurstReelProgressCapRatio</t>
         </is>
       </c>
       <c r="AJ2" s="2" t="inlineStr">
         <is>
-          <t>BurstReelProgressCapRatio</t>
+          <t>BurstReelResistancePenaltyMin</t>
         </is>
       </c>
       <c r="AK2" s="2" t="inlineStr">
         <is>
-          <t>BurstReelResistancePenaltyMin</t>
+          <t>BurstReelResistancePenaltyMax</t>
         </is>
       </c>
       <c r="AL2" s="2" t="inlineStr">
         <is>
-          <t>BurstReelResistancePenaltyMax</t>
+          <t>WeightStaminaLerpMin</t>
         </is>
       </c>
       <c r="AM2" s="2" t="inlineStr">
         <is>
-          <t>WeightStaminaLerpMin</t>
+          <t>WeightStaminaLerpMax</t>
         </is>
       </c>
       <c r="AN2" s="2" t="inlineStr">
         <is>
-          <t>WeightStaminaLerpMax</t>
+          <t>WeightResistanceLerpMin</t>
         </is>
       </c>
       <c r="AO2" s="2" t="inlineStr">
         <is>
-          <t>WeightResistanceLerpMin</t>
+          <t>WeightResistanceLerpMax</t>
         </is>
       </c>
       <c r="AP2" s="2" t="inlineStr">
         <is>
-          <t>WeightResistanceLerpMax</t>
+          <t>WeightEscapeLerpMin</t>
         </is>
       </c>
       <c r="AQ2" s="2" t="inlineStr">
         <is>
-          <t>WeightEscapeLerpMin</t>
+          <t>WeightEscapeLerpMax</t>
         </is>
       </c>
       <c r="AR2" s="2" t="inlineStr">
         <is>
-          <t>WeightEscapeLerpMax</t>
+          <t>SteadyForceLerpWeight</t>
         </is>
       </c>
       <c r="AS2" s="2" t="inlineStr">
         <is>
-          <t>SteadyForceLerpWeight</t>
+          <t>BurstTensionDrainScale</t>
         </is>
       </c>
       <c r="AT2" s="2" t="inlineStr">
         <is>
-          <t>BurstTensionDrainScale</t>
+          <t>FatigueTensionLerpWeight</t>
         </is>
       </c>
       <c r="AU2" s="2" t="inlineStr">
         <is>
-          <t>FatigueTensionLerpWeight</t>
+          <t>SteadyTensionDrainScale</t>
         </is>
       </c>
       <c r="AV2" s="2" t="inlineStr">
         <is>
-          <t>SteadyTensionDrainScale</t>
+          <t>ReelResistanceBase</t>
         </is>
       </c>
       <c r="AW2" s="2" t="inlineStr">
         <is>
-          <t>ReelResistanceBase</t>
+          <t>ReelResistanceDrainScale</t>
         </is>
       </c>
       <c r="AX2" s="2" t="inlineStr">
         <is>
-          <t>ReelResistanceDrainScale</t>
+          <t>BurstReelStruggleScale</t>
         </is>
       </c>
       <c r="AY2" s="2" t="inlineStr">
         <is>
-          <t>BurstReelStruggleScale</t>
+          <t>FatigueReelResistanceFloor</t>
         </is>
       </c>
       <c r="AZ2" s="2" t="inlineStr">
         <is>
-          <t>FatigueReelResistanceFloor</t>
+          <t>FatigueReelResistanceScale</t>
         </is>
       </c>
       <c r="BA2" s="2" t="inlineStr">
         <is>
-          <t>FatigueReelResistanceScale</t>
+          <t>PullForceStaminaLerpMin</t>
         </is>
       </c>
       <c r="BB2" s="2" t="inlineStr">
         <is>
-          <t>PullForceStaminaLerpMin</t>
+          <t>FatigueControlBonus</t>
         </is>
       </c>
       <c r="BC2" s="2" t="inlineStr">
         <is>
-          <t>FatigueControlBonus</t>
+          <t>RelaxBoostScale</t>
         </is>
       </c>
       <c r="BD2" s="2" t="inlineStr">
         <is>
-          <t>RelaxBoostScale</t>
+          <t>EarlyReelSpeedMul</t>
         </is>
       </c>
       <c r="BE2" s="2" t="inlineStr">
         <is>
-          <t>EarlyReelSpeedMul</t>
+          <t>WaitTimeMultiplierFloor</t>
         </is>
       </c>
       <c r="BF2" s="2" t="inlineStr">
         <is>
-          <t>WaitTimeMultiplierFloor</t>
+          <t>ControlSuppressionMax</t>
         </is>
       </c>
       <c r="BG2" s="2" t="inlineStr">
         <is>
-          <t>ControlSuppressionMax</t>
+          <t>SteadyDurationScale</t>
         </is>
       </c>
       <c r="BH2" s="2" t="inlineStr">
-        <is>
-          <t>SteadyDurationScale</t>
-        </is>
-      </c>
-      <c r="BI2" s="2" t="inlineStr">
         <is>
           <t>BaitMismatchWeightScale</t>
         </is>
@@ -1853,140 +1793,137 @@
         <v>0.5</v>
       </c>
       <c r="R3" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="S3" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="T3" s="3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="U3" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="V3" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="W3" s="3" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="X3" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Y3" s="3" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="Z3" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AA3" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AB3" s="3" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC3" s="3" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AD3" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AE3" s="3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AF3" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG3" s="3" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="AH3" s="3" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="AI3" s="3" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="AJ3" s="3" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AK3" s="3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AL3" s="3" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="AM3" s="3" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AN3" s="3" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AO3" s="3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AP3" s="3" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AQ3" s="3" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AR3" s="3" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AS3" s="3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AT3" s="3" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AU3" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AV3" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AW3" s="3" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="AX3" s="3" t="n">
         <v>0.3</v>
       </c>
-      <c r="S3" s="3" t="n">
+      <c r="AY3" s="3" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AZ3" s="3" t="n">
         <v>0.6</v>
       </c>
-      <c r="T3" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="U3" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="V3" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="W3" s="3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X3" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="Y3" s="3" t="n">
+      <c r="BA3" s="3" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="BB3" s="3" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="BC3" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="Z3" s="3" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="AA3" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AB3" s="3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AC3" s="3" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AD3" s="3" t="n">
+      <c r="BD3" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="BE3" s="3" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="BF3" s="3" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="BG3" s="3" t="n">
         <v>0.7</v>
       </c>
-      <c r="AE3" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AF3" s="3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AG3" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="AH3" s="3" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="AI3" s="3" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="AJ3" s="3" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="AK3" s="3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="AL3" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AM3" s="3" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="AN3" s="3" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AO3" s="3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="AP3" s="3" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AQ3" s="3" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="AR3" s="3" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AS3" s="3" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="AT3" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AU3" s="3" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AV3" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="AW3" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AX3" s="3" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="AY3" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="AZ3" s="3" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="BA3" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="BB3" s="3" t="n">
+      <c r="BH3" s="3" t="n">
         <v>0.55</v>
       </c>
-      <c r="BC3" s="3" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="BD3" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="BE3" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="BF3" s="3" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="BG3" s="3" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="BH3" s="3" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="BI3" s="3" t="n">
-        <v>0.55</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:BI3"/>
+  <autoFilter ref="A2:BH3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2298,7 +2235,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T14"/>
+  <dimension ref="A1:S14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2313,14 +2250,13 @@
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="19" customWidth="1" min="11" max="11"/>
     <col width="13" customWidth="1" min="12" max="12"/>
-    <col width="19" customWidth="1" min="13" max="13"/>
+    <col width="21" customWidth="1" min="13" max="13"/>
     <col width="21" customWidth="1" min="14" max="14"/>
-    <col width="21" customWidth="1" min="15" max="15"/>
+    <col width="17" customWidth="1" min="15" max="15"/>
     <col width="17" customWidth="1" min="16" max="16"/>
-    <col width="17" customWidth="1" min="17" max="17"/>
-    <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="17" customWidth="1" min="19" max="19"/>
-    <col width="16" customWidth="1" min="20" max="20"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="17" customWidth="1" min="18" max="18"/>
+    <col width="16" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2386,40 +2322,35 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>推荐鱼竿等级</t>
+          <t>挣扎最短时长</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>挣扎最短时长</t>
+          <t>挣扎最长时长</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>挣扎最长时长</t>
+          <t>休息最短时长</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>休息最短时长</t>
+          <t>休息最长时长</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>休息最长时长</t>
+          <t>冲刺概率</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>冲刺概率</t>
+          <t>基础消耗每秒</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>基础消耗每秒</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>恢复每秒</t>
         </is>
@@ -2488,40 +2419,35 @@
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>RecommendRodLevel</t>
+          <t>StruggleDurationMin</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>StruggleDurationMin</t>
+          <t>StruggleDurationMax</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>StruggleDurationMax</t>
+          <t>RestDurationMin</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>RestDurationMin</t>
+          <t>RestDurationMax</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>RestDurationMax</t>
+          <t>SprintChance</t>
         </is>
       </c>
       <c r="R2" s="2" t="inlineStr">
         <is>
-          <t>SprintChance</t>
+          <t>BaseDrainPerSec</t>
         </is>
       </c>
       <c r="S2" s="2" t="inlineStr">
-        <is>
-          <t>BaseDrainPerSec</t>
-        </is>
-      </c>
-      <c r="T2" s="2" t="inlineStr">
         <is>
           <t>RecoveryPerSec</t>
         </is>
@@ -2571,27 +2497,24 @@
         <v>20</v>
       </c>
       <c r="M3" s="3" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="N3" s="3" t="n">
-        <v>1.8</v>
+        <v>2.8</v>
       </c>
       <c r="O3" s="3" t="n">
-        <v>2.8</v>
+        <v>1.5</v>
       </c>
       <c r="P3" s="3" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="Q3" s="3" t="n">
-        <v>2.5</v>
+        <v>0.1</v>
       </c>
       <c r="R3" s="3" t="n">
-        <v>0.1</v>
+        <v>4.5</v>
       </c>
       <c r="S3" s="3" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="T3" s="3" t="n">
         <v>3.2</v>
       </c>
     </row>
@@ -2639,27 +2562,24 @@
         <v>16</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>2</v>
+        <v>3.2</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>3.2</v>
+        <v>1.2</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>1.2</v>
+        <v>2.2</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>2.2</v>
+        <v>0.2</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>0.2</v>
+        <v>4.2</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="T4" s="3" t="n">
         <v>2.8</v>
       </c>
     </row>
@@ -2707,27 +2627,24 @@
         <v>16</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>3</v>
+        <v>1.2</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>1.2</v>
+        <v>2.2</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>2.2</v>
+        <v>0.18</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>0.18</v>
+        <v>4</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="T5" s="3" t="n">
         <v>2.9</v>
       </c>
     </row>
@@ -2775,27 +2692,24 @@
         <v>18</v>
       </c>
       <c r="M6" s="3" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="O6" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="N6" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="O6" s="3" t="n">
-        <v>3.2</v>
-      </c>
       <c r="P6" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>2</v>
+        <v>0.25</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>0.25</v>
+        <v>4.3</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="T6" s="3" t="n">
         <v>2.7</v>
       </c>
     </row>
@@ -2843,27 +2757,24 @@
         <v>12</v>
       </c>
       <c r="M7" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="O7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="P7" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="N7" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="O7" s="3" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="P7" s="3" t="n">
-        <v>1</v>
-      </c>
       <c r="Q7" s="3" t="n">
-        <v>2</v>
+        <v>0.3</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>0.3</v>
+        <v>4.5</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="T7" s="3" t="n">
         <v>2.4</v>
       </c>
     </row>
@@ -2911,27 +2822,24 @@
         <v>11</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>2.5</v>
+        <v>3.8</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>3.8</v>
+        <v>1</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>1.8</v>
+        <v>0.32</v>
       </c>
       <c r="R8" s="3" t="n">
-        <v>0.32</v>
+        <v>4.8</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="T8" s="3" t="n">
         <v>2.2</v>
       </c>
     </row>
@@ -2979,27 +2887,24 @@
         <v>7</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>2.8</v>
+        <v>4</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>4</v>
+        <v>0.8</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>0.8</v>
+        <v>1.8</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>1.8</v>
+        <v>0.38</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>0.38</v>
+        <v>5.2</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="T9" s="3" t="n">
         <v>2</v>
       </c>
     </row>
@@ -3047,27 +2952,24 @@
         <v>12</v>
       </c>
       <c r="M10" s="3" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="N10" s="3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="O10" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="P10" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="N10" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="O10" s="3" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="P10" s="3" t="n">
-        <v>1</v>
-      </c>
       <c r="Q10" s="3" t="n">
-        <v>2</v>
+        <v>0.28</v>
       </c>
       <c r="R10" s="3" t="n">
-        <v>0.28</v>
+        <v>4.3</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="T10" s="3" t="n">
         <v>2.5</v>
       </c>
     </row>
@@ -3118,24 +3020,21 @@
         <v>3</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>3</v>
+        <v>4.2</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>4.2</v>
+        <v>0.8</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>1.6</v>
+        <v>0.4</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>0.4</v>
+        <v>5.5</v>
       </c>
       <c r="S11" s="3" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="T11" s="3" t="n">
         <v>1.9</v>
       </c>
     </row>
@@ -3186,24 +3085,21 @@
         <v>2</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>2</v>
+        <v>3.2</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>3.2</v>
+        <v>1.2</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>1.2</v>
+        <v>2.2</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>2.2</v>
+        <v>0.22</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0.22</v>
+        <v>4</v>
       </c>
       <c r="S12" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="T12" s="3" t="n">
         <v>2.6</v>
       </c>
     </row>
@@ -3251,27 +3147,24 @@
         <v>5</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>3.2</v>
+        <v>4.5</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>4.5</v>
+        <v>0.8</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="Q13" s="3" t="n">
-        <v>1.5</v>
+        <v>0.45</v>
       </c>
       <c r="R13" s="3" t="n">
-        <v>0.45</v>
+        <v>6.2</v>
       </c>
       <c r="S13" s="3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="T13" s="3" t="n">
         <v>1.7</v>
       </c>
     </row>
@@ -3319,32 +3212,29 @@
         <v>2.5</v>
       </c>
       <c r="M14" s="3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N14" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="N14" s="3" t="n">
-        <v>3.5</v>
-      </c>
       <c r="O14" s="3" t="n">
-        <v>5</v>
+        <v>0.8</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="Q14" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S14" s="3" t="n">
         <v>1.5</v>
       </c>
-      <c r="R14" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="S14" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="T14" s="3" t="n">
-        <v>1.5</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:T14"/>
+  <autoFilter ref="A2:S14"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>